--- a/MAJSushiConfig/ig/StructureDefinition-fr-medication-statement-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-medication-statement-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-statement-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-statement-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -509,7 +509,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-request-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document|0.1.0)
 </t>
   </si>
   <si>
@@ -531,7 +531,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
 </t>
   </si>
   <si>
@@ -641,7 +641,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-document|0.1.0)</t>
+Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document|0.1.0)</t>
   </si>
   <si>
     <t>What medication was taken</t>
@@ -824,7 +824,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0|Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1254,7 +1254,7 @@
     <t>EDQM - Standard terms / classe ROA (0.4.0.127.0.16.1.1.2.1)</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-edqm-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-edqm-document|0.1.0</t>
   </si>
   <si>
     <t>Dosage.route</t>
@@ -1817,7 +1817,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.8046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="103.60546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
